--- a/GenAI/ROADMAP-GenAI.xlsx
+++ b/GenAI/ROADMAP-GenAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\GenAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617DE94E-34D9-4DC0-8F0A-B86AFEB65DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6DDF02-1067-4967-8AB9-7DBF48366457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="210" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="94">
   <si>
     <t>Week</t>
   </si>
@@ -177,9 +177,6 @@
     <t xml:space="preserve"> DALL·E / Stable Diffusion demo </t>
   </si>
   <si>
-    <t xml:space="preserve"> Fine-Tuning Basics </t>
-  </si>
-  <si>
     <t xml:space="preserve"> When to fine-tune vs prompt </t>
   </si>
   <si>
@@ -282,9 +279,6 @@
     <t>X</t>
   </si>
   <si>
-    <t>RAG, Prompt, Full Training, Fine Training</t>
-  </si>
-  <si>
     <t>4 Approaches to LLM(My Add On)</t>
   </si>
   <si>
@@ -304,6 +298,15 @@
   </si>
   <si>
     <t>done in  module Agentic AI</t>
+  </si>
+  <si>
+    <t>RAG, Prompt, Full Training, Fine Tuning</t>
+  </si>
+  <si>
+    <t>PDF done-need refinement</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fine tune-vs-Prompt</t>
   </si>
 </sst>
 </file>
@@ -674,16 +677,16 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -722,42 +725,42 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -811,7 +814,7 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -936,24 +939,27 @@
         <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" t="s">
-        <v>86</v>
-      </c>
       <c r="E19" s="6" t="s">
-        <v>85</v>
+        <v>91</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -973,7 +979,7 @@
         <v>28</v>
       </c>
       <c r="F20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -987,13 +993,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" t="s">
         <v>50</v>
       </c>
-      <c r="E21" t="s">
-        <v>51</v>
-      </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1007,10 +1013,10 @@
         <v>20</v>
       </c>
       <c r="D22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" t="s">
         <v>52</v>
-      </c>
-      <c r="E22" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1030,7 +1036,7 @@
         <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1050,7 +1056,7 @@
         <v>32</v>
       </c>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1070,7 +1076,7 @@
         <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1093,10 +1099,10 @@
         <v>36</v>
       </c>
       <c r="F27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1116,10 +1122,10 @@
         <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1136,13 +1142,13 @@
         <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1162,10 +1168,10 @@
         <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1185,7 +1191,7 @@
         <v>43</v>
       </c>
       <c r="F31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1205,13 +1211,13 @@
         <v>45</v>
       </c>
       <c r="F32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1262,30 +1268,30 @@
         <v>20</v>
       </c>
       <c r="D38" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" t="s">
         <v>54</v>
-      </c>
-      <c r="E38" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" t="s">
         <v>82</v>
       </c>
-      <c r="E39" t="s">
-        <v>83</v>
-      </c>
       <c r="F39" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -1302,16 +1308,16 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" t="s">
         <v>56</v>
       </c>
-      <c r="E41" t="s">
-        <v>57</v>
-      </c>
       <c r="F41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1325,13 +1331,13 @@
         <v>25</v>
       </c>
       <c r="D42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" t="s">
         <v>58</v>
       </c>
-      <c r="E42" t="s">
-        <v>59</v>
-      </c>
       <c r="F42" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1345,13 +1351,13 @@
         <v>25</v>
       </c>
       <c r="D43" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" t="s">
         <v>60</v>
       </c>
-      <c r="E43" t="s">
-        <v>61</v>
-      </c>
       <c r="F43" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1365,13 +1371,13 @@
         <v>25</v>
       </c>
       <c r="D44" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" t="s">
         <v>62</v>
       </c>
-      <c r="E44" t="s">
-        <v>63</v>
-      </c>
       <c r="F44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1385,16 +1391,16 @@
         <v>20</v>
       </c>
       <c r="D45" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" t="s">
         <v>64</v>
       </c>
-      <c r="E45" t="s">
-        <v>65</v>
-      </c>
       <c r="F45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1408,10 +1414,10 @@
         <v>15</v>
       </c>
       <c r="D46" t="s">
+        <v>65</v>
+      </c>
+      <c r="E46" t="s">
         <v>66</v>
-      </c>
-      <c r="E46" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">

--- a/GenAI/ROADMAP-GenAI.xlsx
+++ b/GenAI/ROADMAP-GenAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\GenAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6DDF02-1067-4967-8AB9-7DBF48366457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7849310D-12A1-48A0-BA5A-E23869DFE01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="210" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="1950" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="103">
   <si>
     <t>Week</t>
   </si>
@@ -307,6 +307,33 @@
   </si>
   <si>
     <t xml:space="preserve"> Fine tune-vs-Prompt</t>
+  </si>
+  <si>
+    <t>code done</t>
+  </si>
+  <si>
+    <t>PDF done</t>
+  </si>
+  <si>
+    <t>GAN hands on</t>
+  </si>
+  <si>
+    <t>Diffusion demo</t>
+  </si>
+  <si>
+    <t>Done seperatrely</t>
+  </si>
+  <si>
+    <t>done seperately</t>
+  </si>
+  <si>
+    <t>pdf done seperately in  transformers</t>
+  </si>
+  <si>
+    <t>EXTRA- Autoregression Model</t>
+  </si>
+  <si>
+    <t>PDF + Code done</t>
   </si>
 </sst>
 </file>
@@ -650,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -853,6 +880,9 @@
       <c r="E12" t="s">
         <v>17</v>
       </c>
+      <c r="F12" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
@@ -870,6 +900,9 @@
       <c r="E13" t="s">
         <v>19</v>
       </c>
+      <c r="F13" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
@@ -887,6 +920,9 @@
       <c r="E14" t="s">
         <v>21</v>
       </c>
+      <c r="F14" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
@@ -904,6 +940,9 @@
       <c r="E15" t="s">
         <v>23</v>
       </c>
+      <c r="F15" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
@@ -921,6 +960,9 @@
       <c r="E16" t="s">
         <v>25</v>
       </c>
+      <c r="F16" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D17"/>
@@ -1018,6 +1060,9 @@
       <c r="E22" t="s">
         <v>52</v>
       </c>
+      <c r="F22" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
@@ -1239,21 +1284,52 @@
       <c r="E34" t="s">
         <v>47</v>
       </c>
+      <c r="G34" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>5</v>
       </c>
-      <c r="B35" s="5">
+      <c r="D35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>5</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>5</v>
+      </c>
+      <c r="B37" s="5">
         <v>24</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C37" s="5">
         <v>25</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D37" t="s">
         <v>48</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E37" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1261,103 +1337,74 @@
       <c r="A38" s="5">
         <v>5</v>
       </c>
-      <c r="B38" s="5">
+      <c r="D38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>5</v>
+      </c>
+      <c r="B40" s="5">
         <v>27</v>
       </c>
-      <c r="C38" s="5">
-        <v>20</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C40" s="5">
+        <v>20</v>
+      </c>
+      <c r="D40" t="s">
         <v>53</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E40" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D41" t="s">
         <v>81</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E41" t="s">
         <v>82</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F41" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D40"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
-        <v>6</v>
-      </c>
-      <c r="B41" s="5">
-        <v>28</v>
-      </c>
-      <c r="C41" s="5">
-        <v>20</v>
-      </c>
-      <c r="D41" t="s">
-        <v>55</v>
-      </c>
-      <c r="E41" t="s">
-        <v>56</v>
-      </c>
-      <c r="F41" t="s">
-        <v>90</v>
-      </c>
-      <c r="G41" t="s">
-        <v>76</v>
-      </c>
-    </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
-        <v>6</v>
-      </c>
-      <c r="B42" s="5">
-        <v>29</v>
-      </c>
-      <c r="C42" s="5">
-        <v>25</v>
-      </c>
-      <c r="D42" t="s">
-        <v>57</v>
-      </c>
-      <c r="E42" t="s">
-        <v>58</v>
-      </c>
-      <c r="F42" t="s">
-        <v>90</v>
-      </c>
+      <c r="D42"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>6</v>
       </c>
       <c r="B43" s="5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C43" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E43" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F43" t="s">
         <v>90</v>
+      </c>
+      <c r="G43" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1365,19 +1412,19 @@
         <v>6</v>
       </c>
       <c r="B44" s="5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C44" s="5">
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F44" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1385,22 +1432,19 @@
         <v>6</v>
       </c>
       <c r="B45" s="5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C45" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E45" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F45" t="s">
-        <v>72</v>
-      </c>
-      <c r="G45" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1408,23 +1452,60 @@
         <v>6</v>
       </c>
       <c r="B46" s="5">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>25</v>
+      </c>
+      <c r="D46" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" t="s">
+        <v>62</v>
+      </c>
+      <c r="F46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>6</v>
+      </c>
+      <c r="B47" s="5">
+        <v>32</v>
+      </c>
+      <c r="C47" s="5">
+        <v>20</v>
+      </c>
+      <c r="D47" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" t="s">
+        <v>72</v>
+      </c>
+      <c r="G47" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>6</v>
+      </c>
+      <c r="B48" s="5">
         <v>33</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C48" s="5">
         <v>15</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D48" t="s">
         <v>65</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E48" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D47"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D48"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D49"/>
@@ -1539,6 +1620,12 @@
     </row>
     <row r="86" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D86"/>
+    </row>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D87"/>
+    </row>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D88"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GenAI/ROADMAP-GenAI.xlsx
+++ b/GenAI/ROADMAP-GenAI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\GenAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7849310D-12A1-48A0-BA5A-E23869DFE01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F3E19B-0525-4787-8812-ED96A29B7F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="1950" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="510" yWindow="915" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="105">
   <si>
     <t>Week</t>
   </si>
@@ -334,6 +334,12 @@
   </si>
   <si>
     <t>PDF + Code done</t>
+  </si>
+  <si>
+    <t>llamaindex (EXTRA)</t>
+  </si>
+  <si>
+    <t>pdf+code done</t>
   </si>
 </sst>
 </file>
@@ -677,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -1266,71 +1272,54 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D33"/>
+      <c r="A33" s="5">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
-        <v>5</v>
-      </c>
-      <c r="B34" s="5">
-        <v>23</v>
-      </c>
-      <c r="C34" s="5">
-        <v>20</v>
-      </c>
-      <c r="D34" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" t="s">
-        <v>47</v>
-      </c>
-      <c r="G34" t="s">
-        <v>95</v>
-      </c>
+      <c r="D34"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
-        <v>5</v>
-      </c>
-      <c r="D35" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G35" t="s">
-        <v>94</v>
-      </c>
+      <c r="D35"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>5</v>
       </c>
+      <c r="B36" s="5">
+        <v>23</v>
+      </c>
+      <c r="C36" s="5">
+        <v>20</v>
+      </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>97</v>
+      <c r="E36" t="s">
+        <v>47</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>5</v>
       </c>
-      <c r="B37" s="5">
-        <v>24</v>
-      </c>
-      <c r="C37" s="5">
-        <v>25</v>
-      </c>
       <c r="D37" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G37" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1338,113 +1327,104 @@
         <v>5</v>
       </c>
       <c r="D38" t="s">
-        <v>101</v>
+        <v>46</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="G38" t="s">
-        <v>102</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>5</v>
+      </c>
+      <c r="B39" s="5">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>25</v>
+      </c>
+      <c r="D39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>5</v>
       </c>
-      <c r="B40" s="5">
+      <c r="D40" t="s">
+        <v>101</v>
+      </c>
+      <c r="G40" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>5</v>
+      </c>
+      <c r="B42" s="5">
         <v>27</v>
       </c>
-      <c r="C40" s="5">
-        <v>20</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C42" s="5">
+        <v>20</v>
+      </c>
+      <c r="D42" t="s">
         <v>53</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E42" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B43" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D43" t="s">
         <v>81</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E43" t="s">
         <v>82</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F43" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D42"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
-        <v>6</v>
-      </c>
-      <c r="B43" s="5">
-        <v>28</v>
-      </c>
-      <c r="C43" s="5">
-        <v>20</v>
-      </c>
-      <c r="D43" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F43" t="s">
-        <v>90</v>
-      </c>
-      <c r="G43" t="s">
-        <v>76</v>
-      </c>
-    </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
-        <v>6</v>
-      </c>
-      <c r="B44" s="5">
-        <v>29</v>
-      </c>
-      <c r="C44" s="5">
-        <v>25</v>
-      </c>
-      <c r="D44" t="s">
-        <v>57</v>
-      </c>
-      <c r="E44" t="s">
-        <v>58</v>
-      </c>
-      <c r="F44" t="s">
-        <v>90</v>
-      </c>
+      <c r="D44"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>6</v>
       </c>
       <c r="B45" s="5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C45" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F45" t="s">
         <v>90</v>
+      </c>
+      <c r="G45" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1452,19 +1432,19 @@
         <v>6</v>
       </c>
       <c r="B46" s="5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C46" s="5">
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E46" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F46" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1472,22 +1452,19 @@
         <v>6</v>
       </c>
       <c r="B47" s="5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C47" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E47" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F47" t="s">
-        <v>72</v>
-      </c>
-      <c r="G47" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1495,64 +1472,101 @@
         <v>6</v>
       </c>
       <c r="B48" s="5">
+        <v>31</v>
+      </c>
+      <c r="C48" s="5">
+        <v>25</v>
+      </c>
+      <c r="D48" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" t="s">
+        <v>62</v>
+      </c>
+      <c r="F48" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>6</v>
+      </c>
+      <c r="B49" s="5">
+        <v>32</v>
+      </c>
+      <c r="C49" s="5">
+        <v>20</v>
+      </c>
+      <c r="D49" t="s">
+        <v>63</v>
+      </c>
+      <c r="E49" t="s">
+        <v>64</v>
+      </c>
+      <c r="F49" t="s">
+        <v>72</v>
+      </c>
+      <c r="G49" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>6</v>
+      </c>
+      <c r="B50" s="5">
         <v>33</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C50" s="5">
         <v>15</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D50" t="s">
         <v>65</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E50" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D49"/>
-    </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D50"/>
-    </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D51"/>
     </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D52"/>
     </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D53"/>
     </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D54"/>
     </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D55"/>
     </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D56"/>
     </row>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D57"/>
     </row>
-    <row r="58" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D58"/>
     </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D59"/>
     </row>
-    <row r="60" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D60"/>
     </row>
-    <row r="61" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D61"/>
     </row>
-    <row r="62" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D62"/>
     </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D63"/>
     </row>
-    <row r="64" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D64"/>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.25">
@@ -1626,6 +1640,12 @@
     </row>
     <row r="88" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D88"/>
+    </row>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D89"/>
+    </row>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D90"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GenAI/ROADMAP-GenAI.xlsx
+++ b/GenAI/ROADMAP-GenAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\GenAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F3E19B-0525-4787-8812-ED96A29B7F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5A3706-73B0-48AC-BFF2-4B1CF06621FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="915" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="2055" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="107">
   <si>
     <t>Week</t>
   </si>
@@ -340,6 +340,12 @@
   </si>
   <si>
     <t>pdf+code done</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Guardrails</t>
   </si>
 </sst>
 </file>
@@ -683,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -1365,8 +1371,8 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
-        <v>5</v>
+      <c r="A42" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B42" s="5">
         <v>27</v>
@@ -1402,49 +1408,46 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D44"/>
+      <c r="A44" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
-        <v>6</v>
-      </c>
-      <c r="B45" s="5">
-        <v>28</v>
-      </c>
-      <c r="C45" s="5">
-        <v>20</v>
-      </c>
-      <c r="D45" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" t="s">
-        <v>56</v>
-      </c>
-      <c r="F45" t="s">
-        <v>90</v>
-      </c>
-      <c r="G45" t="s">
-        <v>76</v>
-      </c>
+      <c r="D45"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>6</v>
       </c>
       <c r="B46" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F46" t="s">
         <v>90</v>
+      </c>
+      <c r="G46" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1452,16 +1455,16 @@
         <v>6</v>
       </c>
       <c r="B47" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C47" s="5">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F47" t="s">
         <v>90</v>
@@ -1472,19 +1475,19 @@
         <v>6</v>
       </c>
       <c r="B48" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C48" s="5">
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F48" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1492,22 +1495,19 @@
         <v>6</v>
       </c>
       <c r="B49" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C49" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E49" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F49" t="s">
         <v>72</v>
-      </c>
-      <c r="G49" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1515,20 +1515,40 @@
         <v>6</v>
       </c>
       <c r="B50" s="5">
+        <v>32</v>
+      </c>
+      <c r="C50" s="5">
+        <v>20</v>
+      </c>
+      <c r="D50" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50" t="s">
+        <v>64</v>
+      </c>
+      <c r="F50" t="s">
+        <v>72</v>
+      </c>
+      <c r="G50" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>6</v>
+      </c>
+      <c r="B51" s="5">
         <v>33</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C51" s="5">
         <v>15</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>65</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E51" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D51"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D52"/>
@@ -1646,6 +1666,9 @@
     </row>
     <row r="90" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D90"/>
+    </row>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D91"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
